--- a/data/filtered/china_music.xlsx
+++ b/data/filtered/china_music.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,31 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>是否春节档</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>是否国庆档</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>是否五一档</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>是否暑期档</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>是否普通周末</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>详情链接</t>
         </is>
       </c>
@@ -498,7 +523,22 @@
           <t>2019-03-01</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27060077/</t>
         </is>
@@ -539,7 +579,22 @@
           <t>2001-09-04</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308086/</t>
         </is>
@@ -580,7 +635,22 @@
           <t>2016-05-06</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10831445/</t>
         </is>
@@ -621,7 +691,22 @@
           <t>2007-07-31</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2124724/</t>
         </is>
@@ -662,7 +747,22 @@
           <t>1982</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3804492/</t>
         </is>
@@ -703,7 +803,22 @@
           <t>1985-08-10</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1291876/</t>
         </is>
@@ -744,7 +859,22 @@
           <t>1991-08-29</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308424/</t>
         </is>
@@ -785,7 +915,22 @@
           <t>1999-10-10</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3732861/</t>
         </is>
@@ -826,7 +971,22 @@
           <t>1995-07-22</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1304826/</t>
         </is>
@@ -867,7 +1027,22 @@
           <t>2002-09-20</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1307702/</t>
         </is>
@@ -908,7 +1083,22 @@
           <t>1964-03-21</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1937380/</t>
         </is>
@@ -949,7 +1139,22 @@
           <t>2017-07-20</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26790961/</t>
         </is>
@@ -990,7 +1195,22 @@
           <t>2001-10-25</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1298213/</t>
         </is>
@@ -1027,7 +1247,22 @@
           <t>2002-08-18</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26946280/</t>
         </is>
@@ -1068,7 +1303,22 @@
           <t>2021-04-01</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35420003/</t>
         </is>
@@ -1109,7 +1359,22 @@
           <t>1961</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1498716/</t>
         </is>
@@ -1150,7 +1415,22 @@
           <t>2014-10-17</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4842877/</t>
         </is>
@@ -1191,7 +1471,22 @@
           <t>2016-07-08</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25749813/</t>
         </is>
@@ -1232,7 +1527,22 @@
           <t>2021-11-12</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30176790/</t>
         </is>
@@ -1273,7 +1583,22 @@
           <t>1971-09-16</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1996651/</t>
         </is>
@@ -1314,7 +1639,22 @@
           <t>2006-04-20</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1779509/</t>
         </is>
@@ -1355,7 +1695,22 @@
           <t>2017-09-29</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26926321/</t>
         </is>
@@ -1396,7 +1751,22 @@
           <t>1983-02-12</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593905/</t>
         </is>
@@ -1437,7 +1807,22 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4018191/</t>
         </is>
@@ -1478,7 +1863,22 @@
           <t>2014-01-10</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20388242/</t>
         </is>
@@ -1519,7 +1919,22 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6560928/</t>
         </is>
@@ -1560,7 +1975,22 @@
           <t>2011-11-18</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6126445/</t>
         </is>
@@ -1601,7 +2031,22 @@
           <t>2012-10-12</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6126441/</t>
         </is>
@@ -1642,7 +2087,22 @@
           <t>2017-06-30</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27041519/</t>
         </is>
@@ -1683,7 +2143,22 @@
           <t>1998-01-27</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593951/</t>
         </is>
@@ -1724,7 +2199,22 @@
           <t>1979</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1483903/</t>
         </is>
@@ -1765,7 +2255,22 @@
           <t>2021-04-09</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30359474/</t>
         </is>
@@ -1806,7 +2311,22 @@
           <t>1999-02-15</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593953/</t>
         </is>
@@ -1847,7 +2367,22 @@
           <t>2016-02-22</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26733890/</t>
         </is>
@@ -1888,7 +2423,22 @@
           <t>2013-12-30</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35044539/</t>
         </is>
@@ -1929,7 +2479,22 @@
           <t>2009-01-25</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26594000/</t>
         </is>
@@ -1970,7 +2535,22 @@
           <t>1984-02-02</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593907/</t>
         </is>
@@ -2011,7 +2591,22 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4314336/</t>
         </is>
@@ -2052,7 +2647,22 @@
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35202354/</t>
         </is>
@@ -2093,7 +2703,22 @@
           <t>2013-02-09</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20422192/</t>
         </is>
@@ -2134,7 +2759,22 @@
           <t>2000-02-04</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6101655/</t>
         </is>
@@ -2175,7 +2815,22 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2269967/</t>
         </is>
@@ -2216,7 +2871,22 @@
           <t>2005-02-08</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593965/</t>
         </is>
@@ -2257,7 +2927,22 @@
           <t>2016-03-09</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26890949/</t>
         </is>
@@ -2298,7 +2983,22 @@
           <t>2007-09-21</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2279821/</t>
         </is>
@@ -2339,7 +3039,22 @@
           <t>2008-02-06</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593970/</t>
         </is>
@@ -2380,7 +3095,22 @@
           <t>2010-04-09</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4262170/</t>
         </is>
@@ -2421,7 +3151,22 @@
           <t>2018-09-11</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/33446692/</t>
         </is>
@@ -2462,7 +3207,22 @@
           <t>1990-01-26</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593924/</t>
         </is>
@@ -2503,7 +3263,22 @@
           <t>1995-02-18</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593936/</t>
         </is>
@@ -2544,7 +3319,22 @@
           <t>2001-01-23</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593957/</t>
         </is>
@@ -2585,7 +3375,22 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3532293/</t>
         </is>
@@ -2626,7 +3431,22 @@
           <t>2006-08-17</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1908385/</t>
         </is>
@@ -2667,7 +3487,22 @@
           <t>2012-08-16</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6068517/</t>
         </is>
@@ -2708,7 +3543,22 @@
           <t>2014-01-30</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26594013/</t>
         </is>
@@ -2749,7 +3599,22 @@
           <t>1996-02-18</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593941/</t>
         </is>
@@ -2790,7 +3655,22 @@
           <t>1976-05-23</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4917844/</t>
         </is>
@@ -2831,7 +3711,22 @@
           <t>2010-02-13</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26594004/</t>
         </is>
@@ -2872,7 +3767,22 @@
           <t>2016-08-20</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26891306/</t>
         </is>
@@ -2913,7 +3823,22 @@
           <t>2002-02-11</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593959/</t>
         </is>
@@ -2954,7 +3879,22 @@
           <t>1997-02-06</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593946/</t>
         </is>
@@ -2995,7 +3935,22 @@
           <t>2013-02-09</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26594010/</t>
         </is>
@@ -3036,7 +3991,22 @@
           <t>2006-01-28</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593967/</t>
         </is>
@@ -3077,7 +4047,22 @@
           <t>1988</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1299005/</t>
         </is>
@@ -3118,7 +4103,22 @@
           <t>2003-01-31</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593961/</t>
         </is>
@@ -3159,7 +4159,22 @@
           <t>2012-01-22</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26594009/</t>
         </is>
@@ -3200,7 +4215,22 @@
           <t>1993-01-22</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593931/</t>
         </is>
@@ -3241,7 +4271,22 @@
           <t>1989-02-05</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1</v>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593922/</t>
         </is>
@@ -3282,7 +4327,22 @@
           <t>2008-03-14</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3003092/</t>
         </is>
@@ -3323,7 +4383,22 @@
           <t>1964-06-18</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2033962/</t>
         </is>
@@ -3364,7 +4439,22 @@
           <t>2004-01-21</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593962/</t>
         </is>
@@ -3405,7 +4495,22 @@
           <t>1986-02-08</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593911/</t>
         </is>
@@ -3446,7 +4551,22 @@
           <t>2013-12-13</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20451471/</t>
         </is>
@@ -3487,7 +4607,22 @@
           <t>2009-09-06</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4074063/</t>
         </is>
@@ -3528,7 +4663,22 @@
           <t>2012-04-19</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/7055667/</t>
         </is>
@@ -3569,7 +4719,22 @@
           <t>1992-02-02</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593928/</t>
         </is>
@@ -3610,7 +4775,22 @@
           <t>1959</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26437092/</t>
         </is>
@@ -3651,7 +4831,22 @@
           <t>2007-02-17</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593969/</t>
         </is>
@@ -3692,7 +4887,22 @@
           <t>1987-01-28</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593914/</t>
         </is>
@@ -3733,7 +4943,22 @@
           <t>2011-02-02</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26594007/</t>
         </is>
@@ -3774,7 +4999,22 @@
           <t>1991-02-14</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593926/</t>
         </is>
@@ -3815,7 +5055,22 @@
           <t>2015-03-20</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35196723/</t>
         </is>
@@ -3856,7 +5111,22 @@
           <t>1988-02-16</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593915/</t>
         </is>
@@ -3897,7 +5167,22 @@
           <t>2009-03-27</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3552307/</t>
         </is>
@@ -3938,7 +5223,22 @@
           <t>2017-12-07</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26895406/</t>
         </is>
@@ -3979,7 +5279,22 @@
           <t>1994-02-09</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593935/</t>
         </is>
@@ -4020,7 +5335,22 @@
           <t>1985-02-19</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593909/</t>
         </is>
@@ -4061,7 +5391,22 @@
           <t>2017-12-25</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27602185/</t>
         </is>
@@ -4102,7 +5447,22 @@
           <t>2000-09-17</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1302254/</t>
         </is>
@@ -4143,7 +5503,22 @@
           <t>2016-06-01</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26890963/</t>
         </is>
@@ -4184,7 +5559,22 @@
           <t>2023-10-19</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36191463/</t>
         </is>
@@ -4225,7 +5615,22 @@
           <t>2005-01-01</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1</v>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1476255/</t>
         </is>
@@ -4266,7 +5671,22 @@
           <t>2010-04-30</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4223304/</t>
         </is>
@@ -4307,7 +5727,22 @@
           <t>2018-01-01</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27620588/</t>
         </is>
@@ -4348,7 +5783,22 @@
           <t>2011-09-02</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5319823/</t>
         </is>
@@ -4389,7 +5839,22 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11527607/</t>
         </is>
@@ -4430,7 +5895,22 @@
           <t>2009-01-09</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3141456/</t>
         </is>
@@ -4471,7 +5951,22 @@
           <t>2016-12-31</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1</v>
+      </c>
+      <c r="N99" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26946404/</t>
         </is>
@@ -4512,7 +6007,22 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10468706/</t>
         </is>
@@ -4553,7 +6063,22 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30394576/</t>
         </is>
@@ -4594,7 +6119,22 @@
           <t>2018-11-02</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26985916/</t>
         </is>
@@ -4635,7 +6175,22 @@
           <t>2018-09-14</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27073366/</t>
         </is>
@@ -4676,7 +6231,22 @@
           <t>2019-05-17</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27187926/</t>
         </is>
@@ -4717,7 +6287,22 @@
           <t>2015-06-20</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1</v>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25706778/</t>
         </is>
@@ -4758,7 +6343,22 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6815113/</t>
         </is>
@@ -4799,7 +6399,22 @@
           <t>2022-02-25</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35657302/</t>
         </is>
@@ -4840,7 +6455,22 @@
           <t>2019-07-26</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>1</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26921076/</t>
         </is>
@@ -4881,7 +6511,22 @@
           <t>2016-02-22</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26696182/</t>
         </is>
@@ -4922,7 +6567,22 @@
           <t>2011-11-17</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6971298/</t>
         </is>
@@ -4963,7 +6623,22 @@
           <t>2011-11-24</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6068516/</t>
         </is>
@@ -5004,7 +6679,22 @@
           <t>2012-09-21</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10759842/</t>
         </is>
@@ -5045,7 +6735,22 @@
           <t>2013-02-02</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1</v>
+      </c>
+      <c r="N113" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5161713/</t>
         </is>
@@ -5086,7 +6791,22 @@
           <t>2015-11-27</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25919327/</t>
         </is>
@@ -5127,7 +6847,22 @@
           <t>2012-04-13</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6755902/</t>
         </is>
@@ -5168,7 +6903,22 @@
           <t>2013-12-27</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25741108/</t>
         </is>
